--- a/Assets/Data/Commodore/C64/250425/Data C64 250425 v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C64/250425/Data C64 250425 v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Commodore\C64\250425\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C64\250425\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D17513-A67F-485F-8D1F-ABC7CC1A32E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92761F2-F857-49E7-BB2C-138E07E1CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13025" uniqueCount="3634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13030" uniqueCount="3638">
   <si>
     <r>
       <t xml:space="preserve"># Hardware: </t>
@@ -11025,6 +11025,27 @@
     <t>Commodore/Shared files/Component local files/8701.pdf</t>
   </si>
   <si>
+    <t>Forum64; Repair Corner (primarily German)</t>
+  </si>
+  <si>
+    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
+  </si>
+  <si>
+    <t>8e4b6290-1cb3-44b0-a422-925d27304090</t>
+  </si>
+  <si>
+    <t>6.3x32mm, Flink</t>
+  </si>
+  <si>
+    <t>Zimmers; Character ROMs</t>
+  </si>
+  <si>
+    <t>https://www.zimmers.net/anonftp/pub/cbm/firmware/characters/</t>
+  </si>
+  <si>
+    <t>61bc83c1-4960-43ba-96ac-7ccda068adc8</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -11036,17 +11057,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026-May-12</t>
+      <t>2026-June-10</t>
     </r>
-  </si>
-  <si>
-    <t>Forum64; Repair Corner (primarily German)</t>
-  </si>
-  <si>
-    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
-  </si>
-  <si>
-    <t>8e4b6290-1cb3-44b0-a422-925d27304090</t>
   </si>
 </sst>
 </file>
@@ -11695,7 +11707,7 @@
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" ht="21">
       <c r="A3" s="10" t="s">
-        <v>3630</v>
+        <v>3637</v>
       </c>
       <c r="I3"/>
     </row>
@@ -14443,6 +14455,9 @@
       <c r="E120" s="1" t="s">
         <v>398</v>
       </c>
+      <c r="G120" s="1" t="s">
+        <v>3633</v>
+      </c>
       <c r="H120" t="s">
         <v>399</v>
       </c>
@@ -16094,7 +16109,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -62271,7 +62286,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -62370,46 +62385,46 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>308</v>
-      </c>
-      <c r="B12" t="s">
-        <v>965</v>
-      </c>
-      <c r="C12" t="s">
-        <v>966</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>2418</v>
+    <row r="12" spans="1:4" s="56" customFormat="1">
+      <c r="A12" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>3634</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>3635</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>3636</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="B13" t="s">
-        <v>1054</v>
+        <v>965</v>
       </c>
       <c r="C13" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2419</v>
+        <v>966</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>2418</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C14" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D14" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -62417,66 +62432,77 @@
         <v>355</v>
       </c>
       <c r="B15" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>355</v>
+      </c>
+      <c r="B16" t="s">
         <v>2492</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>2493</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>2494</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="56" customFormat="1">
-      <c r="A16" s="56" t="s">
+    <row r="17" spans="1:4" s="56" customFormat="1">
+      <c r="A17" s="56" t="s">
         <v>424</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B17" s="56" t="s">
         <v>2489</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C17" s="56" t="s">
         <v>2490</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>2491</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="21"/>
-      <c r="D20" s="1"/>
-    </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="24"/>
+      <c r="A21" s="21"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4">
+      <c r="A22" s="24"/>
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4">
       <c r="D23" s="1"/>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="22"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="22"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="23"/>
+    <row r="24" spans="1:4">
+      <c r="D24" s="1"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="22"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="22"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="11"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="D37" s="50"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="D39" s="50"/>
-    </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="5"/>
-    </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="1"/>
+      <c r="A33" s="23"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="11"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="D38" s="50"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="D40" s="50"/>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="5"/>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="1"/>
@@ -62489,6 +62515,9 @@
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -62961,13 +62990,13 @@
         <v>1024</v>
       </c>
       <c r="B22" t="s">
+        <v>3630</v>
+      </c>
+      <c r="C22" t="s">
         <v>3631</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>3632</v>
-      </c>
-      <c r="D22" t="s">
-        <v>3633</v>
       </c>
     </row>
     <row r="23" spans="1:4">
